--- a/02_HRvLR/05_Module_Preservation/c_data/module_preservation.xlsx
+++ b/02_HRvLR/05_Module_Preservation/c_data/module_preservation.xlsx
@@ -6436,7 +6436,7 @@
     <t>corrected</t>
   </si>
   <si>
-    <t>01_Processing/03_Blood_Correction/c_data/proteins_corrected.rds</t>
+    <t>01_Processing/03_Blood_Correction/c_data/blood_correction.rds</t>
   </si>
   <si>
     <t>35fac30909b3ec9c4ae9469c4edc26a0</t>
@@ -6445,7 +6445,7 @@
     <t>modules</t>
   </si>
   <si>
-    <t>01_Processing/06_Module_Building/c_data/modules.rds</t>
+    <t>01_Processing/06_Module_Building/c_data/module_building.rds</t>
   </si>
   <si>
     <t>32c36eae09056636394bdb0714dd608a</t>
